--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 32 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 144 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10742503.15</v>
+        <v>10742658.33</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-4526645.74</v>
+        <v>-501520.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>679.9</v>
+        <v>679.8200000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-333.77</v>
+        <v>23.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.17</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.043</v>
+        <v>-0.0779</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.043</v>
+        <v>-0.0779</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1876</v>
+        <v>-0.1493</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1876</v>
+        <v>0.1493</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.0293</v>
+        <v>0.0992</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>229781.52</v>
+        <v>229946.56</v>
       </c>
       <c r="I2" t="n">
         <v>1.37</v>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>182725.51</v>
+        <v>182704.58</v>
       </c>
       <c r="I3" t="n">
         <v>1.38</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>83221.24000000001</v>
+        <v>83211.56</v>
       </c>
       <c r="I4" t="n">
         <v>1.36</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>74010.64</v>
+        <v>74002.07000000001</v>
       </c>
       <c r="I5" t="n">
         <v>1.37</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>52455.59</v>
+        <v>52449.56</v>
       </c>
       <c r="I6" t="n">
         <v>1.38</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>73305.25</v>
+        <v>73297.78999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1.56</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>74572.52</v>
+        <v>74565.86</v>
       </c>
       <c r="I8" t="n">
         <v>1.78</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>34763.78</v>
+        <v>34760.76</v>
       </c>
       <c r="I9" t="n">
         <v>1.83</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>64939.71</v>
+        <v>64933.68</v>
       </c>
       <c r="I10" t="n">
         <v>1.71</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>128403.37</v>
+        <v>128401.47</v>
       </c>
       <c r="I11" t="n">
         <v>10.7</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>26728.22</v>
+        <v>26725.69</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>114999.71</v>
+        <v>114990.51</v>
       </c>
       <c r="I13" t="n">
         <v>1.98</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>39008.98</v>
+        <v>39005.65</v>
       </c>
       <c r="I14" t="n">
         <v>1.86</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>59442.26</v>
+        <v>59437.18</v>
       </c>
       <c r="I15" t="n">
         <v>1.86</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>33436.27</v>
+        <v>33433.42</v>
       </c>
       <c r="I16" t="n">
         <v>1.86</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>48365.52</v>
+        <v>48361.71</v>
       </c>
       <c r="I17" t="n">
         <v>2.02</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>124296.78</v>
+        <v>124295.03</v>
       </c>
       <c r="I18" t="n">
         <v>11.3</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>85053.21000000001</v>
+        <v>85046.23</v>
       </c>
       <c r="I19" t="n">
         <v>1.93</v>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>73187.03999999999</v>
+        <v>73180.85000000001</v>
       </c>
       <c r="I20" t="n">
         <v>1.88</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>52544.54</v>
+        <v>52540.1</v>
       </c>
       <c r="I21" t="n">
         <v>1.88</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>58174.31</v>
+        <v>58169.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.88</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>98048.3</v>
+        <v>98046.87</v>
       </c>
       <c r="I23" t="n">
         <v>10.89</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>92601.17</v>
+        <v>92599.83</v>
       </c>
       <c r="I24" t="n">
         <v>10.89</v>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>14074.43</v>
+        <v>14073.24</v>
       </c>
       <c r="I25" t="n">
         <v>1.88</v>
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>113180.63</v>
+        <v>113170.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.83</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2656,7 +2656,7 @@
         <v>0.3473</v>
       </c>
       <c r="H27" t="n">
-        <v>36578.11</v>
+        <v>36576.51</v>
       </c>
       <c r="I27" t="n">
         <v>1.26</v>
@@ -2724,7 +2724,7 @@
         <v>0.3473</v>
       </c>
       <c r="H28" t="n">
-        <v>26488.09</v>
+        <v>26486.93</v>
       </c>
       <c r="I28" t="n">
         <v>1.26</v>
@@ -2792,7 +2792,7 @@
         <v>0.3473</v>
       </c>
       <c r="H29" t="n">
-        <v>30270.04</v>
+        <v>30268.72</v>
       </c>
       <c r="I29" t="n">
         <v>1.26</v>
@@ -2860,7 +2860,7 @@
         <v>0.3473</v>
       </c>
       <c r="H30" t="n">
-        <v>17661.13</v>
+        <v>17660.36</v>
       </c>
       <c r="I30" t="n">
         <v>1.26</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>31033.4</v>
+        <v>31030.7</v>
       </c>
       <c r="I31" t="n">
         <v>1.83</v>
@@ -2996,7 +2996,7 @@
         <v>0.3472</v>
       </c>
       <c r="H32" t="n">
-        <v>18916.97</v>
+        <v>18916.15</v>
       </c>
       <c r="I32" t="n">
         <v>1.26</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>143946.17</v>
+        <v>143934.91</v>
       </c>
       <c r="I33" t="n">
         <v>2.03</v>
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>44603.04</v>
+        <v>44599.55</v>
       </c>
       <c r="I34" t="n">
         <v>2.03</v>
@@ -3200,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>26356.34</v>
+        <v>26354.28</v>
       </c>
       <c r="I35" t="n">
         <v>2.03</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>110794.82</v>
+        <v>110793.23</v>
       </c>
       <c r="I36" t="n">
         <v>11.08</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>22301.52</v>
+        <v>22299.77</v>
       </c>
       <c r="I37" t="n">
         <v>2.03</v>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>28383.75</v>
+        <v>28381.53</v>
       </c>
       <c r="I38" t="n">
         <v>2.03</v>
@@ -3456,23 +3456,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>289312.99</v>
+        <v>290040.4</v>
       </c>
       <c r="I39" t="n">
         <v>1.54</v>
@@ -3496,7 +3496,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>94162.58</v>
+        <v>94154.02</v>
       </c>
       <c r="I40" t="n">
         <v>1.74</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>56532.79</v>
+        <v>56527.88</v>
       </c>
       <c r="I41" t="n">
         <v>1.82</v>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>83036.71000000001</v>
+        <v>83030.05</v>
       </c>
       <c r="I42" t="n">
         <v>1.98</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>71628.27</v>
+        <v>71622.56</v>
       </c>
       <c r="I43" t="n">
         <v>1.99</v>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>202917.42</v>
+        <v>202914.41</v>
       </c>
       <c r="I44" t="n">
         <v>10.68</v>
@@ -3880,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>33610.1</v>
+        <v>33607.4</v>
       </c>
       <c r="I45" t="n">
         <v>1.98</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>39621.84</v>
+        <v>39618.19</v>
       </c>
       <c r="I46" t="n">
         <v>1.72</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>158768.06</v>
+        <v>158752.83</v>
       </c>
       <c r="I47" t="n">
         <v>1.65</v>
@@ -4084,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>87594.07000000001</v>
+        <v>87587.56</v>
       </c>
       <c r="I48" t="n">
         <v>2.14</v>
@@ -4152,7 +4152,7 @@
         <v>0.7161999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>42900.49</v>
+        <v>42897.53</v>
       </c>
       <c r="I49" t="n">
         <v>1.65</v>
@@ -4220,7 +4220,7 @@
         <v>0.8951</v>
       </c>
       <c r="H50" t="n">
-        <v>43381.52</v>
+        <v>43378.39</v>
       </c>
       <c r="I50" t="n">
         <v>1.97</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>55310.53</v>
+        <v>55306.09</v>
       </c>
       <c r="I51" t="n">
         <v>1.98</v>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>125527.33</v>
+        <v>125525.43</v>
       </c>
       <c r="I52" t="n">
         <v>10.46</v>
@@ -4424,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>159455.09</v>
+        <v>159452.87</v>
       </c>
       <c r="I53" t="n">
         <v>11.39</v>
@@ -4492,7 +4492,7 @@
         <v>0.5039</v>
       </c>
       <c r="H54" t="n">
-        <v>96714.52</v>
+        <v>96707.48</v>
       </c>
       <c r="I54" t="n">
         <v>1.1</v>
@@ -4560,7 +4560,7 @@
         <v>0.5039</v>
       </c>
       <c r="H55" t="n">
-        <v>57146.83</v>
+        <v>57142.68</v>
       </c>
       <c r="I55" t="n">
         <v>1.1</v>
@@ -4628,7 +4628,7 @@
         <v>0.5039</v>
       </c>
       <c r="H56" t="n">
-        <v>48357.26</v>
+        <v>48353.74</v>
       </c>
       <c r="I56" t="n">
         <v>1.1</v>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>67704.96000000001</v>
+        <v>67701.14999999999</v>
       </c>
       <c r="I57" t="n">
         <v>2.82</v>
@@ -4764,7 +4764,7 @@
         <v>0.5039</v>
       </c>
       <c r="H58" t="n">
-        <v>36266.73</v>
+        <v>36264.09</v>
       </c>
       <c r="I58" t="n">
         <v>1.1</v>
@@ -4832,7 +4832,7 @@
         <v>0.5039</v>
       </c>
       <c r="H59" t="n">
-        <v>29674.55</v>
+        <v>29672.39</v>
       </c>
       <c r="I59" t="n">
         <v>1.1</v>
@@ -4900,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>42315.6</v>
+        <v>42313.22</v>
       </c>
       <c r="I60" t="n">
         <v>2.82</v>
@@ -4968,7 +4968,7 @@
         <v>0.5039</v>
       </c>
       <c r="H61" t="n">
-        <v>51653.35</v>
+        <v>51649.59</v>
       </c>
       <c r="I61" t="n">
         <v>1.1</v>
@@ -5036,7 +5036,7 @@
         <v>0.5039</v>
       </c>
       <c r="H62" t="n">
-        <v>42858.91</v>
+        <v>42855.79</v>
       </c>
       <c r="I62" t="n">
         <v>1.1</v>
@@ -5104,7 +5104,7 @@
         <v>0.5039</v>
       </c>
       <c r="H63" t="n">
-        <v>26378.45</v>
+        <v>26376.54</v>
       </c>
       <c r="I63" t="n">
         <v>1.1</v>
@@ -5172,7 +5172,7 @@
         <v>0.5038</v>
       </c>
       <c r="H64" t="n">
-        <v>24176.2</v>
+        <v>24174.44</v>
       </c>
       <c r="I64" t="n">
         <v>1.1</v>
@@ -5240,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>230189.59</v>
+        <v>230186.74</v>
       </c>
       <c r="I65" t="n">
         <v>12.79</v>
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>152445.19</v>
+        <v>152443.13</v>
       </c>
       <c r="I66" t="n">
         <v>11.73</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>140671.42</v>
+        <v>140669.67</v>
       </c>
       <c r="I67" t="n">
         <v>12.79</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>135760.77</v>
+        <v>135749.2</v>
       </c>
       <c r="I68" t="n">
         <v>1.89</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>86981.72</v>
+        <v>86974.02</v>
       </c>
       <c r="I69" t="n">
         <v>1.81</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>76963.41</v>
+        <v>76957.3</v>
       </c>
       <c r="I70" t="n">
         <v>2.03</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>88206.63</v>
+        <v>88200.03999999999</v>
       </c>
       <c r="I71" t="n">
         <v>2.15</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>55633.09</v>
+        <v>55628.44</v>
       </c>
       <c r="I72" t="n">
         <v>1.92</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>63067.51</v>
+        <v>63062.37</v>
       </c>
       <c r="I73" t="n">
         <v>1.97</v>
@@ -5852,7 +5852,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>184698.13</v>
+        <v>184684.64</v>
       </c>
       <c r="I74" t="n">
         <v>2.2</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>98460.34</v>
+        <v>98453.42999999999</v>
       </c>
       <c r="I75" t="n">
         <v>2.29</v>
@@ -5988,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>69557.89999999999</v>
+        <v>69552.92</v>
       </c>
       <c r="I76" t="n">
         <v>2.24</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>56743.36</v>
+        <v>56739.02</v>
       </c>
       <c r="I77" t="n">
         <v>2.1</v>
@@ -6124,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>192067.52</v>
+        <v>192064.95</v>
       </c>
       <c r="I78" t="n">
         <v>12</v>
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>149535.23</v>
+        <v>149522.55</v>
       </c>
       <c r="I79" t="n">
         <v>1.89</v>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>81044.8</v>
+        <v>81037.74000000001</v>
       </c>
       <c r="I80" t="n">
         <v>1.84</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>70072.58</v>
+        <v>70066.78999999999</v>
       </c>
       <c r="I81" t="n">
         <v>1.95</v>
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>79116.00999999999</v>
+        <v>79109.75</v>
       </c>
       <c r="I82" t="n">
         <v>2.03</v>
@@ -6464,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>46287.23</v>
+        <v>46283.53</v>
       </c>
       <c r="I83" t="n">
         <v>2.01</v>
@@ -6532,10 +6532,10 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>52784.21</v>
+        <v>52779.72</v>
       </c>
       <c r="I84" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>187117.37</v>
+        <v>187099.39</v>
       </c>
       <c r="I85" t="n">
         <v>1.67</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>61106.1</v>
+        <v>61100.64</v>
       </c>
       <c r="I86" t="n">
         <v>1.8</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>56199.52</v>
+        <v>56194.55</v>
       </c>
       <c r="I87" t="n">
         <v>1.81</v>
@@ -6804,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>38572.21</v>
+        <v>38568.67</v>
       </c>
       <c r="I88" t="n">
         <v>1.75</v>
@@ -6872,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>44751.18</v>
+        <v>44747</v>
       </c>
       <c r="I89" t="n">
         <v>1.72</v>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>105299.89</v>
+        <v>105290.58</v>
       </c>
       <c r="I90" t="n">
         <v>1.82</v>
@@ -7008,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>73766.62</v>
+        <v>73760.03999999999</v>
       </c>
       <c r="I91" t="n">
         <v>1.8</v>
@@ -7076,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>83979.50999999999</v>
+        <v>83971.97</v>
       </c>
       <c r="I92" t="n">
         <v>1.79</v>
@@ -7144,10 +7144,10 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>45242.12</v>
+        <v>45238.26</v>
       </c>
       <c r="I93" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>197709.24</v>
+        <v>197706.19</v>
       </c>
       <c r="I94" t="n">
         <v>10.41</v>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>142354.91</v>
+        <v>142343.02</v>
       </c>
       <c r="I95" t="n">
         <v>1.92</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>85828.67</v>
+        <v>85821.28999999999</v>
       </c>
       <c r="I96" t="n">
         <v>1.87</v>
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>64764.72</v>
+        <v>64759.42</v>
       </c>
       <c r="I97" t="n">
         <v>1.96</v>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>222716.73</v>
+        <v>222713.35</v>
       </c>
       <c r="I98" t="n">
         <v>10.61</v>
@@ -7552,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>57525.79</v>
+        <v>57521.13</v>
       </c>
       <c r="I99" t="n">
         <v>1.98</v>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>49973.96</v>
+        <v>49969.94</v>
       </c>
       <c r="I100" t="n">
         <v>2</v>
@@ -7667,28 +7667,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>230486.44</v>
+        <v>230394.3</v>
       </c>
       <c r="I101" t="n">
         <v>2.13</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>121223.88</v>
+        <v>121214.05</v>
       </c>
       <c r="I102" t="n">
         <v>1.96</v>
@@ -7824,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>72789.60000000001</v>
+        <v>72784.21000000001</v>
       </c>
       <c r="I103" t="n">
         <v>2.14</v>
@@ -7892,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>71059.24000000001</v>
+        <v>71054.32000000001</v>
       </c>
       <c r="I104" t="n">
         <v>2.29</v>
@@ -7960,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>60233.6</v>
+        <v>60229.16</v>
       </c>
       <c r="I105" t="n">
         <v>2.15</v>
@@ -8028,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>144033.26</v>
+        <v>144031.2</v>
       </c>
       <c r="I106" t="n">
         <v>11.08</v>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>121874.3</v>
+        <v>121872.56</v>
       </c>
       <c r="I107" t="n">
         <v>11.08</v>
@@ -8164,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>96958.14999999999</v>
+        <v>96952.75999999999</v>
       </c>
       <c r="I108" t="n">
         <v>2.85</v>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>25665.39</v>
+        <v>25663.97</v>
       </c>
       <c r="I109" t="n">
         <v>2.85</v>
@@ -8300,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>18536.12</v>
+        <v>18535.09</v>
       </c>
       <c r="I110" t="n">
         <v>2.85</v>
@@ -8368,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>15684.41</v>
+        <v>15683.53</v>
       </c>
       <c r="I111" t="n">
         <v>2.85</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>14258.55</v>
+        <v>14257.76</v>
       </c>
       <c r="I112" t="n">
         <v>2.85</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8504,7 +8504,7 @@
         <v>0.7211</v>
       </c>
       <c r="H113" t="n">
-        <v>95540.36</v>
+        <v>95533.73</v>
       </c>
       <c r="I113" t="n">
         <v>1.65</v>
@@ -8572,7 +8572,7 @@
         <v>0.7211</v>
       </c>
       <c r="H114" t="n">
-        <v>75773.16</v>
+        <v>75767.89999999999</v>
       </c>
       <c r="I114" t="n">
         <v>1.65</v>
@@ -8640,7 +8640,7 @@
         <v>0.5768</v>
       </c>
       <c r="H115" t="n">
-        <v>26092.29</v>
+        <v>26090.55</v>
       </c>
       <c r="I115" t="n">
         <v>1.37</v>
@@ -8708,7 +8708,7 @@
         <v>0.7212</v>
       </c>
       <c r="H116" t="n">
-        <v>28006.32</v>
+        <v>28004.37</v>
       </c>
       <c r="I116" t="n">
         <v>1.65</v>
@@ -8776,7 +8776,7 @@
         <v>0.5768</v>
       </c>
       <c r="H117" t="n">
-        <v>10985.35</v>
+        <v>10984.62</v>
       </c>
       <c r="I117" t="n">
         <v>1.37</v>
@@ -8844,7 +8844,7 @@
         <v>0.5769</v>
       </c>
       <c r="H118" t="n">
-        <v>19228.53</v>
+        <v>19227.25</v>
       </c>
       <c r="I118" t="n">
         <v>1.37</v>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>167961.58</v>
+        <v>167946.98</v>
       </c>
       <c r="I119" t="n">
         <v>1.83</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>107561.6</v>
+        <v>107551.92</v>
       </c>
       <c r="I120" t="n">
         <v>1.76</v>
@@ -9048,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>69728.19</v>
+        <v>69722.16</v>
       </c>
       <c r="I121" t="n">
         <v>1.83</v>
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>37889.9</v>
+        <v>37886.57</v>
       </c>
       <c r="I122" t="n">
         <v>1.8</v>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>55585.03</v>
+        <v>55581.39</v>
       </c>
       <c r="I123" t="n">
         <v>2.42</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>43501.33</v>
+        <v>43498.48</v>
       </c>
       <c r="I124" t="n">
         <v>2.42</v>
@@ -9320,7 +9320,7 @@
         <v>0.971</v>
       </c>
       <c r="H125" t="n">
-        <v>164851.9</v>
+        <v>164839.88</v>
       </c>
       <c r="I125" t="n">
         <v>2.11</v>
@@ -9388,7 +9388,7 @@
         <v>0.971</v>
       </c>
       <c r="H126" t="n">
-        <v>67629.95</v>
+        <v>67625.03</v>
       </c>
       <c r="I126" t="n">
         <v>2.11</v>
@@ -9456,7 +9456,7 @@
         <v>0.7768</v>
       </c>
       <c r="H127" t="n">
-        <v>28025.3</v>
+        <v>28023.33</v>
       </c>
       <c r="I127" t="n">
         <v>1.75</v>
@@ -9524,7 +9524,7 @@
         <v>0.971</v>
       </c>
       <c r="H128" t="n">
-        <v>86652.03999999999</v>
+        <v>86645.73</v>
       </c>
       <c r="I128" t="n">
         <v>2.11</v>
@@ -9592,7 +9592,7 @@
         <v>0.7769</v>
       </c>
       <c r="H129" t="n">
-        <v>42040.53</v>
+        <v>42037.57</v>
       </c>
       <c r="I129" t="n">
         <v>1.75</v>
@@ -9660,7 +9660,7 @@
         <v>0.7372</v>
       </c>
       <c r="H130" t="n">
-        <v>118167.22</v>
+        <v>118159.38</v>
       </c>
       <c r="I130" t="n">
         <v>1.76</v>
@@ -9728,7 +9728,7 @@
         <v>0.7372</v>
       </c>
       <c r="H131" t="n">
-        <v>91711.95</v>
+        <v>91705.87</v>
       </c>
       <c r="I131" t="n">
         <v>1.76</v>
@@ -9796,7 +9796,7 @@
         <v>0.7372</v>
       </c>
       <c r="H132" t="n">
-        <v>77602.81</v>
+        <v>77597.67</v>
       </c>
       <c r="I132" t="n">
         <v>1.76</v>
@@ -9864,7 +9864,7 @@
         <v>0.7371</v>
       </c>
       <c r="H133" t="n">
-        <v>31744.27</v>
+        <v>31742.16</v>
       </c>
       <c r="I133" t="n">
         <v>1.76</v>
@@ -9932,7 +9932,7 @@
         <v>0.7372</v>
       </c>
       <c r="H134" t="n">
-        <v>12346.14</v>
+        <v>12345.32</v>
       </c>
       <c r="I134" t="n">
         <v>1.76</v>
@@ -10000,7 +10000,7 @@
         <v>0.7372</v>
       </c>
       <c r="H135" t="n">
-        <v>28218.27</v>
+        <v>28216.4</v>
       </c>
       <c r="I135" t="n">
         <v>1.76</v>
@@ -10179,7 +10179,7 @@
         <v>2721.52</v>
       </c>
       <c r="I2" t="n">
-        <v>114313.66</v>
+        <v>114313.64</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -10231,7 +10231,7 @@
         <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>14351.99</v>
+        <v>14351.95</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -10289,7 +10289,7 @@
         <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>21869.71</v>
+        <v>21869.64</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -10347,7 +10347,7 @@
         <v>195.25</v>
       </c>
       <c r="I5" t="n">
-        <v>12301.71</v>
+        <v>12301.67</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -10405,7 +10405,7 @@
         <v>2892.77</v>
       </c>
       <c r="I6" t="n">
-        <v>111381.21</v>
+        <v>111381.19</v>
       </c>
       <c r="J6" t="n">
         <v>255.89</v>
@@ -10457,7 +10457,7 @@
         <v>216.81</v>
       </c>
       <c r="I7" t="n">
-        <v>33390.95</v>
+        <v>33390.86</v>
       </c>
       <c r="J7" t="n">
         <v>538.08</v>
@@ -10515,7 +10515,7 @@
         <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>27395.49</v>
+        <v>27395.41</v>
       </c>
       <c r="J8" t="n">
         <v>1162.1</v>
@@ -10573,7 +10573,7 @@
         <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>19668.56</v>
+        <v>19668.5</v>
       </c>
       <c r="J9" t="n">
         <v>1251.46</v>
@@ -10631,7 +10631,7 @@
         <v>200.68</v>
       </c>
       <c r="I10" t="n">
-        <v>21775.9</v>
+        <v>21775.84</v>
       </c>
       <c r="J10" t="n">
         <v>767.52</v>
@@ -10689,7 +10689,7 @@
         <v>200.68</v>
       </c>
       <c r="I11" t="n">
-        <v>5268.36</v>
+        <v>5268.35</v>
       </c>
       <c r="J11" t="n">
         <v>955.4400000000001</v>
@@ -10747,7 +10747,7 @@
         <v>2776.94</v>
       </c>
       <c r="I12" t="n">
-        <v>87481.02</v>
+        <v>87481</v>
       </c>
       <c r="J12" t="n">
         <v>617.75</v>
@@ -10799,7 +10799,7 @@
         <v>2776.94</v>
       </c>
       <c r="I13" t="n">
-        <v>82620.96000000001</v>
+        <v>82620.95</v>
       </c>
       <c r="J13" t="n">
         <v>684.9400000000001</v>
@@ -10851,7 +10851,7 @@
         <v>186.08</v>
       </c>
       <c r="I14" t="n">
-        <v>40383.81</v>
+        <v>40383.69</v>
       </c>
       <c r="J14" t="n">
         <v>448.61</v>
@@ -10909,7 +10909,7 @@
         <v>186.08</v>
       </c>
       <c r="I15" t="n">
-        <v>11072.98</v>
+        <v>11072.95</v>
       </c>
       <c r="J15" t="n">
         <v>358.09</v>
@@ -10967,7 +10967,7 @@
         <v>702.15</v>
       </c>
       <c r="I16" t="n">
-        <v>24752.82</v>
+        <v>24752.8</v>
       </c>
       <c r="J16" t="n">
         <v>534.23</v>
@@ -11025,7 +11025,7 @@
         <v>702.15</v>
       </c>
       <c r="I17" t="n">
-        <v>17924.79</v>
+        <v>17924.78</v>
       </c>
       <c r="J17" t="n">
         <v>758.5700000000001</v>
@@ -11083,7 +11083,7 @@
         <v>702.15</v>
       </c>
       <c r="I18" t="n">
-        <v>20484.08</v>
+        <v>20484.07</v>
       </c>
       <c r="J18" t="n">
         <v>483.91</v>
@@ -11141,7 +11141,7 @@
         <v>702.15</v>
       </c>
       <c r="I19" t="n">
-        <v>11951.49</v>
+        <v>11951.48</v>
       </c>
       <c r="J19" t="n">
         <v>488.03</v>
@@ -11199,7 +11199,7 @@
         <v>702.15</v>
       </c>
       <c r="I20" t="n">
-        <v>12801.33</v>
+        <v>12801.32</v>
       </c>
       <c r="J20" t="n">
         <v>407.1</v>
@@ -11257,7 +11257,7 @@
         <v>243.77</v>
       </c>
       <c r="I21" t="n">
-        <v>60582.07</v>
+        <v>60581.93</v>
       </c>
       <c r="J21" t="n">
         <v>323.36</v>
@@ -11315,7 +11315,7 @@
         <v>243.77</v>
       </c>
       <c r="I22" t="n">
-        <v>18771.91</v>
+        <v>18771.86</v>
       </c>
       <c r="J22" t="n">
         <v>308.79</v>
@@ -11373,7 +11373,7 @@
         <v>243.77</v>
       </c>
       <c r="I23" t="n">
-        <v>11092.49</v>
+        <v>11092.47</v>
       </c>
       <c r="J23" t="n">
         <v>447.3</v>
@@ -11431,7 +11431,7 @@
         <v>243.77</v>
       </c>
       <c r="I24" t="n">
-        <v>9385.950000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J24" t="n">
         <v>459</v>
@@ -11489,7 +11489,7 @@
         <v>243.77</v>
       </c>
       <c r="I25" t="n">
-        <v>11945.76</v>
+        <v>11945.73</v>
       </c>
       <c r="J25" t="n">
         <v>306.91</v>
@@ -11547,7 +11547,7 @@
         <v>2829.85</v>
       </c>
       <c r="I26" t="n">
-        <v>99053.39999999999</v>
+        <v>99053.38</v>
       </c>
       <c r="J26" t="n">
         <v>315.98</v>
@@ -11599,7 +11599,7 @@
         <v>229.39</v>
       </c>
       <c r="I27" t="n">
-        <v>33722.74</v>
+        <v>33722.65</v>
       </c>
       <c r="J27" t="n">
         <v>117.11</v>
@@ -11657,7 +11657,7 @@
         <v>229.39</v>
       </c>
       <c r="I28" t="n">
-        <v>13649.68</v>
+        <v>13649.65</v>
       </c>
       <c r="J28" t="n">
         <v>106.12</v>
@@ -11715,7 +11715,7 @@
         <v>2715.69</v>
       </c>
       <c r="I29" t="n">
-        <v>180608.72</v>
+        <v>180608.68</v>
       </c>
       <c r="J29" t="n">
         <v>64.55</v>
@@ -11767,7 +11767,7 @@
         <v>322.79</v>
       </c>
       <c r="I30" t="n">
-        <v>21037.87</v>
+        <v>21037.83</v>
       </c>
       <c r="J30" t="n">
         <v>106.06</v>
@@ -11825,7 +11825,7 @@
         <v>293.91</v>
       </c>
       <c r="I31" t="n">
-        <v>20259.54</v>
+        <v>20259.5</v>
       </c>
       <c r="J31" t="n">
         <v>80.93000000000001</v>
@@ -11883,7 +11883,7 @@
         <v>2653.05</v>
       </c>
       <c r="I32" t="n">
-        <v>111437.63</v>
+        <v>111437.6</v>
       </c>
       <c r="J32" t="n">
         <v>98.78</v>
@@ -11935,7 +11935,7 @@
         <v>2918.47</v>
       </c>
       <c r="I33" t="n">
-        <v>143017.1</v>
+        <v>143017.07</v>
       </c>
       <c r="J33" t="n">
         <v>139.33</v>
@@ -11987,7 +11987,7 @@
         <v>287.67</v>
       </c>
       <c r="I34" t="n">
-        <v>44649.8</v>
+        <v>44649.71</v>
       </c>
       <c r="J34" t="n">
         <v>364.01</v>
@@ -12045,7 +12045,7 @@
         <v>287.67</v>
       </c>
       <c r="I35" t="n">
-        <v>26382.75</v>
+        <v>26382.7</v>
       </c>
       <c r="J35" t="n">
         <v>428.56</v>
@@ -12103,7 +12103,7 @@
         <v>287.67</v>
       </c>
       <c r="I36" t="n">
-        <v>22324.9</v>
+        <v>22324.86</v>
       </c>
       <c r="J36" t="n">
         <v>280.66</v>
@@ -12161,7 +12161,7 @@
         <v>287.67</v>
       </c>
       <c r="I37" t="n">
-        <v>16743.11</v>
+        <v>16743.08</v>
       </c>
       <c r="J37" t="n">
         <v>390.59</v>
@@ -12219,7 +12219,7 @@
         <v>287.67</v>
       </c>
       <c r="I38" t="n">
-        <v>13699.73</v>
+        <v>13699.7</v>
       </c>
       <c r="J38" t="n">
         <v>405.44</v>
@@ -12277,7 +12277,7 @@
         <v>287.67</v>
       </c>
       <c r="I39" t="n">
-        <v>23846.59</v>
+        <v>23846.55</v>
       </c>
       <c r="J39" t="n">
         <v>698.29</v>
@@ -12335,7 +12335,7 @@
         <v>287.67</v>
       </c>
       <c r="I40" t="n">
-        <v>19786.5</v>
+        <v>19786.46</v>
       </c>
       <c r="J40" t="n">
         <v>544.61</v>
@@ -12393,7 +12393,7 @@
         <v>287.67</v>
       </c>
       <c r="I41" t="n">
-        <v>12178.03</v>
+        <v>12178.01</v>
       </c>
       <c r="J41" t="n">
         <v>560.1</v>
@@ -12451,7 +12451,7 @@
         <v>287.67</v>
       </c>
       <c r="I42" t="n">
-        <v>11161.33</v>
+        <v>11161.31</v>
       </c>
       <c r="J42" t="n">
         <v>494.37</v>
@@ -12509,7 +12509,7 @@
         <v>470.5</v>
       </c>
       <c r="I43" t="n">
-        <v>39525.54</v>
+        <v>39525.49</v>
       </c>
       <c r="J43" t="n">
         <v>532.85</v>
@@ -12567,7 +12567,7 @@
         <v>470.5</v>
       </c>
       <c r="I44" t="n">
-        <v>24703.46</v>
+        <v>24703.43</v>
       </c>
       <c r="J44" t="n">
         <v>426.83</v>
@@ -12625,7 +12625,7 @@
         <v>3318.05</v>
       </c>
       <c r="I45" t="n">
-        <v>209055.03</v>
+        <v>209055</v>
       </c>
       <c r="J45" t="n">
         <v>460.47</v>
@@ -12677,7 +12677,7 @@
         <v>3014.72</v>
       </c>
       <c r="I46" t="n">
-        <v>137181.34</v>
+        <v>137181.31</v>
       </c>
       <c r="J46" t="n">
         <v>538.6799999999999</v>
@@ -12729,7 +12729,7 @@
         <v>3318.05</v>
       </c>
       <c r="I47" t="n">
-        <v>127755.85</v>
+        <v>127755.83</v>
       </c>
       <c r="J47" t="n">
         <v>395.68</v>
@@ -12781,7 +12781,7 @@
         <v>3094.04</v>
       </c>
       <c r="I48" t="n">
-        <v>173281.24</v>
+        <v>173281.18</v>
       </c>
       <c r="J48" t="n">
         <v>201.21</v>
@@ -12830,10 +12830,10 @@
         <v>66.5057</v>
       </c>
       <c r="H49" t="n">
-        <v>2637.38</v>
+        <v>2637.37</v>
       </c>
       <c r="I49" t="n">
-        <v>175400.54</v>
+        <v>175400.46</v>
       </c>
       <c r="J49" t="n">
         <v>53.72</v>
@@ -12885,7 +12885,7 @@
         <v>2694.46</v>
       </c>
       <c r="I50" t="n">
-        <v>198059.74</v>
+        <v>198059.65</v>
       </c>
       <c r="J50" t="n">
         <v>94.98999999999999</v>
@@ -12937,7 +12937,7 @@
         <v>2829.85</v>
       </c>
       <c r="I51" t="n">
-        <v>128769.41</v>
+        <v>128769.39</v>
       </c>
       <c r="J51" t="n">
         <v>120.54</v>
@@ -12989,7 +12989,7 @@
         <v>2829.85</v>
       </c>
       <c r="I52" t="n">
-        <v>108958.74</v>
+        <v>108958.71</v>
       </c>
       <c r="J52" t="n">
         <v>130.5</v>
@@ -13041,7 +13041,7 @@
         <v>479.26</v>
       </c>
       <c r="I53" t="n">
-        <v>57037.32</v>
+        <v>57037.25</v>
       </c>
       <c r="J53" t="n">
         <v>477.86</v>
@@ -13099,7 +13099,7 @@
         <v>479.26</v>
       </c>
       <c r="I54" t="n">
-        <v>15098.11</v>
+        <v>15098.1</v>
       </c>
       <c r="J54" t="n">
         <v>482.12</v>
@@ -13157,7 +13157,7 @@
         <v>479.26</v>
       </c>
       <c r="I55" t="n">
-        <v>10904.19</v>
+        <v>10904.18</v>
       </c>
       <c r="J55" t="n">
         <v>480.24</v>
@@ -13215,7 +13215,7 @@
         <v>479.26</v>
       </c>
       <c r="I56" t="n">
-        <v>9226.620000000001</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J56" t="n">
         <v>481.26</v>
@@ -13273,7 +13273,7 @@
         <v>479.26</v>
       </c>
       <c r="I57" t="n">
-        <v>8387.84</v>
+        <v>8387.83</v>
       </c>
       <c r="J57" t="n">
         <v>412.79</v>
@@ -13331,7 +13331,7 @@
         <v>317.17</v>
       </c>
       <c r="I58" t="n">
-        <v>46433.08</v>
+        <v>46433</v>
       </c>
       <c r="J58" t="n">
         <v>311.37</v>
@@ -13389,7 +13389,7 @@
         <v>317.17</v>
       </c>
       <c r="I59" t="n">
-        <v>36826.12</v>
+        <v>36826.06</v>
       </c>
       <c r="J59" t="n">
         <v>94.95999999999999</v>
@@ -13447,7 +13447,7 @@
         <v>344.7</v>
       </c>
       <c r="I60" t="n">
-        <v>13223.79</v>
+        <v>13223.77</v>
       </c>
       <c r="J60" t="n">
         <v>182.8</v>
@@ -13505,7 +13505,7 @@
         <v>317.17</v>
       </c>
       <c r="I61" t="n">
-        <v>13611.2</v>
+        <v>13611.18</v>
       </c>
       <c r="J61" t="n">
         <v>175.95</v>
@@ -13563,7 +13563,7 @@
         <v>344.7</v>
       </c>
       <c r="I62" t="n">
-        <v>5567.47</v>
+        <v>5567.46</v>
       </c>
       <c r="J62" t="n">
         <v>205.12</v>
@@ -13621,7 +13621,7 @@
         <v>344.7</v>
       </c>
       <c r="I63" t="n">
-        <v>9745.18</v>
+        <v>9745.16</v>
       </c>
       <c r="J63" t="n">
         <v>368.78</v>
@@ -13679,7 +13679,7 @@
         <v>355</v>
       </c>
       <c r="I64" t="n">
-        <v>28579.76</v>
+        <v>28579.72</v>
       </c>
       <c r="J64" t="n">
         <v>240.83</v>
@@ -13737,7 +13737,7 @@
         <v>355</v>
       </c>
       <c r="I65" t="n">
-        <v>22366.77</v>
+        <v>22366.73</v>
       </c>
       <c r="J65" t="n">
         <v>189.94</v>
@@ -13795,7 +13795,7 @@
         <v>286.36</v>
       </c>
       <c r="I66" t="n">
-        <v>75920.53</v>
+        <v>75920.38</v>
       </c>
       <c r="J66" t="n">
         <v>328.7</v>
@@ -13853,7 +13853,7 @@
         <v>286.36</v>
       </c>
       <c r="I67" t="n">
-        <v>31146.15</v>
+        <v>31146.09</v>
       </c>
       <c r="J67" t="n">
         <v>328.88</v>
@@ -13911,7 +13911,7 @@
         <v>308.74</v>
       </c>
       <c r="I68" t="n">
-        <v>13431.78</v>
+        <v>13431.76</v>
       </c>
       <c r="J68" t="n">
         <v>369.95</v>
@@ -13969,7 +13969,7 @@
         <v>286.36</v>
       </c>
       <c r="I69" t="n">
-        <v>39906.54</v>
+        <v>39906.46</v>
       </c>
       <c r="J69" t="n">
         <v>215.37</v>
@@ -14027,7 +14027,7 @@
         <v>308.74</v>
       </c>
       <c r="I70" t="n">
-        <v>20148.9</v>
+        <v>20148.87</v>
       </c>
       <c r="J70" t="n">
         <v>445.5</v>
@@ -14085,7 +14085,7 @@
         <v>348.06</v>
       </c>
       <c r="I71" t="n">
-        <v>60174.66</v>
+        <v>60174.56</v>
       </c>
       <c r="J71" t="n">
         <v>357.34</v>
@@ -14143,7 +14143,7 @@
         <v>348.06</v>
       </c>
       <c r="I72" t="n">
-        <v>46702.76</v>
+        <v>46702.68</v>
       </c>
       <c r="J72" t="n">
         <v>513.78</v>
@@ -14201,7 +14201,7 @@
         <v>348.06</v>
       </c>
       <c r="I73" t="n">
-        <v>39517.92</v>
+        <v>39517.86</v>
       </c>
       <c r="J73" t="n">
         <v>577.77</v>
@@ -14259,7 +14259,7 @@
         <v>348.06</v>
       </c>
       <c r="I74" t="n">
-        <v>16165.23</v>
+        <v>16165.21</v>
       </c>
       <c r="J74" t="n">
         <v>447.68</v>
@@ -14317,7 +14317,7 @@
         <v>348.06</v>
       </c>
       <c r="I75" t="n">
-        <v>6287.06</v>
+        <v>6287.05</v>
       </c>
       <c r="J75" t="n">
         <v>267.72</v>
@@ -14375,7 +14375,7 @@
         <v>348.06</v>
       </c>
       <c r="I76" t="n">
-        <v>14369.68</v>
+        <v>14369.65</v>
       </c>
       <c r="J76" t="n">
         <v>370.08</v>
@@ -14427,13 +14427,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H77" t="n">
         <v>55.64</v>
       </c>
       <c r="I77" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J77" t="n">
         <v>4.28</v>
@@ -14482,10 +14482,10 @@
         <v>462.0396</v>
       </c>
       <c r="H78" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I78" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J78" t="n">
         <v>13.54</v>
@@ -14537,7 +14537,7 @@
         <v>54.32</v>
       </c>
       <c r="I79" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J79" t="n">
         <v>1.51</v>
@@ -14589,7 +14589,7 @@
         <v>56.12</v>
       </c>
       <c r="I80" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J80" t="n">
         <v>5.29</v>
@@ -14641,7 +14641,7 @@
         <v>58.93</v>
       </c>
       <c r="I81" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J81" t="n">
         <v>11.21</v>
@@ -14693,7 +14693,7 @@
         <v>110.15</v>
       </c>
       <c r="I82" t="n">
-        <v>18120.56</v>
+        <v>18120.47</v>
       </c>
       <c r="J82" t="n">
         <v>103.3</v>
@@ -14745,7 +14745,7 @@
         <v>171.81</v>
       </c>
       <c r="I83" t="n">
-        <v>25258.54</v>
+        <v>25258.46</v>
       </c>
       <c r="J83" t="n">
         <v>171.76</v>
@@ -14797,7 +14797,7 @@
         <v>187.28</v>
       </c>
       <c r="I84" t="n">
-        <v>12455.07</v>
+        <v>12455.04</v>
       </c>
       <c r="J84" t="n">
         <v>218.82</v>
@@ -14849,7 +14849,7 @@
         <v>152.79</v>
       </c>
       <c r="I85" t="n">
-        <v>20322.3</v>
+        <v>20322.22</v>
       </c>
       <c r="J85" t="n">
         <v>183.69</v>
@@ -14901,7 +14901,7 @@
         <v>141.81</v>
       </c>
       <c r="I86" t="n">
-        <v>7941.95</v>
+        <v>7941.92</v>
       </c>
       <c r="J86" t="n">
         <v>125.96</v>
@@ -14953,7 +14953,7 @@
         <v>231.01</v>
       </c>
       <c r="I87" t="n">
-        <v>46899.45</v>
+        <v>46899.34</v>
       </c>
       <c r="J87" t="n">
         <v>331.17</v>
@@ -15005,7 +15005,7 @@
         <v>240.29</v>
       </c>
       <c r="I88" t="n">
-        <v>20186.1</v>
+        <v>20186.05</v>
       </c>
       <c r="J88" t="n">
         <v>276.29</v>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>105.37</v>
+        <v>105.36</v>
       </c>
       <c r="I89" t="n">
-        <v>69156.57000000001</v>
+        <v>69331.11</v>
       </c>
       <c r="J89" t="n">
         <v>1.06</v>
@@ -15109,7 +15109,7 @@
         <v>162.73</v>
       </c>
       <c r="I90" t="n">
-        <v>30758.9</v>
+        <v>30758.79</v>
       </c>
       <c r="J90" t="n">
         <v>113.39</v>
@@ -15161,7 +15161,7 @@
         <v>185.55</v>
       </c>
       <c r="I91" t="n">
-        <v>20134.38</v>
+        <v>20134.32</v>
       </c>
       <c r="J91" t="n">
         <v>129.6</v>
@@ -15213,7 +15213,7 @@
         <v>232.99</v>
       </c>
       <c r="I92" t="n">
-        <v>29359.15</v>
+        <v>29359.08</v>
       </c>
       <c r="J92" t="n">
         <v>209.49</v>
@@ -15265,7 +15265,7 @@
         <v>156.71</v>
       </c>
       <c r="I93" t="n">
-        <v>12616.57</v>
+        <v>12616.52</v>
       </c>
       <c r="J93" t="n">
         <v>101.42</v>
@@ -15317,7 +15317,7 @@
         <v>137.04</v>
       </c>
       <c r="I94" t="n">
-        <v>46050.4</v>
+        <v>46050.21</v>
       </c>
       <c r="J94" t="n">
         <v>1.39</v>
@@ -15369,7 +15369,7 @@
         <v>274.92</v>
       </c>
       <c r="I95" t="n">
-        <v>39454.23</v>
+        <v>39454.15</v>
       </c>
       <c r="J95" t="n">
         <v>202.79</v>
@@ -15421,7 +15421,7 @@
         <v>228.9</v>
       </c>
       <c r="I96" t="n">
-        <v>22434.55</v>
+        <v>22434.49</v>
       </c>
       <c r="J96" t="n">
         <v>132.55</v>
@@ -15473,7 +15473,7 @@
         <v>203.25</v>
       </c>
       <c r="I97" t="n">
-        <v>51222.52</v>
+        <v>51222.24</v>
       </c>
       <c r="J97" t="n">
         <v>122.66</v>
@@ -15525,7 +15525,7 @@
         <v>182.26</v>
       </c>
       <c r="I98" t="n">
-        <v>30622.9</v>
+        <v>30622.71</v>
       </c>
       <c r="J98" t="n">
         <v>80.92</v>
@@ -15577,7 +15577,7 @@
         <v>243.18</v>
       </c>
       <c r="I99" t="n">
-        <v>32346</v>
+        <v>32345.85</v>
       </c>
       <c r="J99" t="n">
         <v>166.27</v>
@@ -15629,7 +15629,7 @@
         <v>279.19</v>
       </c>
       <c r="I100" t="n">
-        <v>40066.79</v>
+        <v>40066.63</v>
       </c>
       <c r="J100" t="n">
         <v>226.91</v>
@@ -15681,7 +15681,7 @@
         <v>212.62</v>
       </c>
       <c r="I101" t="n">
-        <v>21582.97</v>
+        <v>21582.85</v>
       </c>
       <c r="J101" t="n">
         <v>114.8</v>
@@ -15733,7 +15733,7 @@
         <v>227.61</v>
       </c>
       <c r="I102" t="n">
-        <v>25494.96</v>
+        <v>25494.83</v>
       </c>
       <c r="J102" t="n">
         <v>140.05</v>
@@ -15785,7 +15785,7 @@
         <v>292.73</v>
       </c>
       <c r="I103" t="n">
-        <v>86070.17999999999</v>
+        <v>86069.84</v>
       </c>
       <c r="J103" t="n">
         <v>249.72</v>
@@ -15837,7 +15837,7 @@
         <v>318.72</v>
       </c>
       <c r="I104" t="n">
-        <v>47972.22</v>
+        <v>47972.05</v>
       </c>
       <c r="J104" t="n">
         <v>293.5</v>
@@ -15889,7 +15889,7 @@
         <v>305.59</v>
       </c>
       <c r="I105" t="n">
-        <v>33159.49</v>
+        <v>33159.37</v>
       </c>
       <c r="J105" t="n">
         <v>271.38</v>
@@ -15941,7 +15941,7 @@
         <v>264.97</v>
       </c>
       <c r="I106" t="n">
-        <v>25041.51</v>
+        <v>25041.41</v>
       </c>
       <c r="J106" t="n">
         <v>202.96</v>
@@ -15993,7 +15993,7 @@
         <v>205.33</v>
       </c>
       <c r="I107" t="n">
-        <v>56778</v>
+        <v>56777.68</v>
       </c>
       <c r="J107" t="n">
         <v>126.8</v>
@@ -16045,7 +16045,7 @@
         <v>190.78</v>
       </c>
       <c r="I108" t="n">
-        <v>29382.55</v>
+        <v>29382.37</v>
       </c>
       <c r="J108" t="n">
         <v>97.86</v>
@@ -16097,7 +16097,7 @@
         <v>220.64</v>
       </c>
       <c r="I109" t="n">
-        <v>27803.45</v>
+        <v>27803.31</v>
       </c>
       <c r="J109" t="n">
         <v>128.31</v>
@@ -16149,7 +16149,7 @@
         <v>244.11</v>
       </c>
       <c r="I110" t="n">
-        <v>33324.47</v>
+        <v>33324.31</v>
       </c>
       <c r="J110" t="n">
         <v>167.84</v>
@@ -16201,7 +16201,7 @@
         <v>239.51</v>
       </c>
       <c r="I111" t="n">
-        <v>19281.95</v>
+        <v>19281.86</v>
       </c>
       <c r="J111" t="n">
         <v>160.08</v>
@@ -16253,7 +16253,7 @@
         <v>203.13</v>
       </c>
       <c r="I112" t="n">
-        <v>19908.23</v>
+        <v>19908.12</v>
       </c>
       <c r="J112" t="n">
         <v>98.81</v>
@@ -16305,7 +16305,7 @@
         <v>141.86</v>
       </c>
       <c r="I113" t="n">
-        <v>55613.44</v>
+        <v>55613</v>
       </c>
       <c r="J113" t="n">
         <v>2.42</v>
@@ -16357,7 +16357,7 @@
         <v>178.01</v>
       </c>
       <c r="I114" t="n">
-        <v>21185.26</v>
+        <v>21185.13</v>
       </c>
       <c r="J114" t="n">
         <v>56.51</v>
@@ -16409,7 +16409,7 @@
         <v>182.48</v>
       </c>
       <c r="I115" t="n">
-        <v>19801.11</v>
+        <v>19800.99</v>
       </c>
       <c r="J115" t="n">
         <v>64.04000000000001</v>
@@ -16461,7 +16461,7 @@
         <v>165.45</v>
       </c>
       <c r="I116" t="n">
-        <v>12741.08</v>
+        <v>12740.99</v>
       </c>
       <c r="J116" t="n">
         <v>35.36</v>
@@ -16513,7 +16513,7 @@
         <v>156.29</v>
       </c>
       <c r="I117" t="n">
-        <v>14223.48</v>
+        <v>14223.38</v>
       </c>
       <c r="J117" t="n">
         <v>29.25</v>
@@ -16565,7 +16565,7 @@
         <v>183.23</v>
       </c>
       <c r="I118" t="n">
-        <v>37199.64</v>
+        <v>37199.41</v>
       </c>
       <c r="J118" t="n">
         <v>82.84999999999999</v>
@@ -16617,7 +16617,7 @@
         <v>178.57</v>
       </c>
       <c r="I119" t="n">
-        <v>25626.79</v>
+        <v>25626.63</v>
       </c>
       <c r="J119" t="n">
         <v>73.56999999999999</v>
@@ -16669,7 +16669,7 @@
         <v>175.03</v>
       </c>
       <c r="I120" t="n">
-        <v>28794.83</v>
+        <v>28794.64</v>
       </c>
       <c r="J120" t="n">
         <v>66.53</v>
@@ -16721,7 +16721,7 @@
         <v>203.11</v>
       </c>
       <c r="I121" t="n">
-        <v>17062.7</v>
+        <v>17062.61</v>
       </c>
       <c r="J121" t="n">
         <v>98.78</v>
@@ -16770,10 +16770,10 @@
         <v>259.0222</v>
       </c>
       <c r="H122" t="n">
-        <v>214.15</v>
+        <v>214.14</v>
       </c>
       <c r="I122" t="n">
-        <v>55468.38</v>
+        <v>55468.09</v>
       </c>
       <c r="J122" t="n">
         <v>144.34</v>
@@ -16825,7 +16825,7 @@
         <v>197.61</v>
       </c>
       <c r="I123" t="n">
-        <v>31818.13</v>
+        <v>31817.95</v>
       </c>
       <c r="J123" t="n">
         <v>111.45</v>
@@ -16877,7 +16877,7 @@
         <v>225.24</v>
       </c>
       <c r="I124" t="n">
-        <v>26018.03</v>
+        <v>26017.89</v>
       </c>
       <c r="J124" t="n">
         <v>136.06</v>
@@ -16929,7 +16929,7 @@
         <v>231.27</v>
       </c>
       <c r="I125" t="n">
-        <v>23475.67</v>
+        <v>23475.55</v>
       </c>
       <c r="J125" t="n">
         <v>178.4</v>
@@ -16981,7 +16981,7 @@
         <v>235.64</v>
       </c>
       <c r="I126" t="n">
-        <v>20620.4</v>
+        <v>20620.3</v>
       </c>
       <c r="J126" t="n">
         <v>153.57</v>
@@ -17027,13 +17027,13 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H127" t="n">
         <v>274.06</v>
       </c>
       <c r="I127" t="n">
-        <v>103637.48</v>
+        <v>103603.85</v>
       </c>
       <c r="J127" t="n">
         <v>334.85</v>
@@ -17085,7 +17085,7 @@
         <v>223.15</v>
       </c>
       <c r="I128" t="n">
-        <v>48427.06</v>
+        <v>48426.94</v>
       </c>
       <c r="J128" t="n">
         <v>233.57</v>
@@ -17137,7 +17137,7 @@
         <v>276.18</v>
       </c>
       <c r="I129" t="n">
-        <v>32868.77</v>
+        <v>32868.7</v>
       </c>
       <c r="J129" t="n">
         <v>282.24</v>
@@ -17189,7 +17189,7 @@
         <v>319.43</v>
       </c>
       <c r="I130" t="n">
-        <v>34660.83</v>
+        <v>34660.77</v>
       </c>
       <c r="J130" t="n">
         <v>355.07</v>
@@ -17238,10 +17238,10 @@
         <v>98.00839999999999</v>
       </c>
       <c r="H131" t="n">
-        <v>279.14</v>
+        <v>279.13</v>
       </c>
       <c r="I131" t="n">
-        <v>27357.61</v>
+        <v>27357.56</v>
       </c>
       <c r="J131" t="n">
         <v>287.21</v>
@@ -17293,7 +17293,7 @@
         <v>186.13</v>
       </c>
       <c r="I132" t="n">
-        <v>59940.49</v>
+        <v>59940.31</v>
       </c>
       <c r="J132" t="n">
         <v>31.5</v>
@@ -17345,7 +17345,7 @@
         <v>168.32</v>
       </c>
       <c r="I133" t="n">
-        <v>35938.92</v>
+        <v>35938.8</v>
       </c>
       <c r="J133" t="n">
         <v>1.35</v>
@@ -17397,7 +17397,7 @@
         <v>188.79</v>
       </c>
       <c r="I134" t="n">
-        <v>25110.79</v>
+        <v>25110.71</v>
       </c>
       <c r="J134" t="n">
         <v>36.5</v>
@@ -17449,7 +17449,7 @@
         <v>180.02</v>
       </c>
       <c r="I135" t="n">
-        <v>13232.92</v>
+        <v>13232.87</v>
       </c>
       <c r="J135" t="n">
         <v>19.98</v>
@@ -17563,16 +17563,16 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1620948.95</v>
+        <v>1621733.87</v>
       </c>
       <c r="H5" t="n">
         <v>1.57</v>
@@ -17603,7 +17603,7 @@
         <v>0.9072</v>
       </c>
       <c r="G6" t="n">
-        <v>1589661.56</v>
+        <v>1589527.43</v>
       </c>
       <c r="H6" t="n">
         <v>1.72</v>
@@ -17634,7 +17634,7 @@
         <v>0.9791</v>
       </c>
       <c r="G7" t="n">
-        <v>1885659.91</v>
+        <v>1885504.14</v>
       </c>
       <c r="H7" t="n">
         <v>1.89</v>
@@ -17656,19 +17656,19 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2933.2</v>
+        <v>2933.1</v>
       </c>
       <c r="F8" t="n">
         <v>0.8661</v>
       </c>
       <c r="G8" t="n">
-        <v>1804515.89</v>
+        <v>1804307.52</v>
       </c>
       <c r="H8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I8" t="n">
         <v>0.3065</v>
@@ -17696,7 +17696,7 @@
         <v>0.8507</v>
       </c>
       <c r="G9" t="n">
-        <v>3841716.84</v>
+        <v>3841585.37</v>
       </c>
       <c r="H9" t="n">
         <v>3.95</v>
@@ -17741,7 +17741,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 24,500 PGK · annual change -4,526,646 PGK · payback 0.01 years</t>
+          <t>One-off cost 24,500 PGK · annual change -501,520 PGK · payback 0.05 years</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 144 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 92 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9291296.029999999</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9664</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12116356.02</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 92 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 68 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 68 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 43 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 42 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 42 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 46 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 46 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 55 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 55 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 91 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 91 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 56 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 56 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 76 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 76 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 43 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-5.xlsx
+++ b/docs/app/api/files/results-5.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 46 ms</t>
         </is>
       </c>
     </row>
